--- a/artfynd/A 28816-2023 artfynd.xlsx
+++ b/artfynd/A 28816-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130659216</v>
       </c>
       <c r="B2" t="n">
-        <v>58224</v>
+        <v>58226</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 28816-2023 artfynd.xlsx
+++ b/artfynd/A 28816-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130659216</v>
       </c>
       <c r="B2" t="n">
-        <v>58226</v>
+        <v>58234</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 28816-2023 artfynd.xlsx
+++ b/artfynd/A 28816-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130659216</v>
       </c>
       <c r="B2" t="n">
-        <v>58234</v>
+        <v>58235</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 28816-2023 artfynd.xlsx
+++ b/artfynd/A 28816-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130659216</v>
       </c>
       <c r="B2" t="n">
-        <v>58235</v>
+        <v>58236</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 28816-2023 artfynd.xlsx
+++ b/artfynd/A 28816-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130659216</v>
       </c>
       <c r="B2" t="n">
-        <v>58256</v>
+        <v>58327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 28816-2023 artfynd.xlsx
+++ b/artfynd/A 28816-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AZ2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -777,8 +782,16 @@
           <t>NVI Sika 4:37</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130659216</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 28816-2023 artfynd.xlsx
+++ b/artfynd/A 28816-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,10 +680,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130659216</v>
+        <v>136480652</v>
       </c>
       <c r="B2" t="n">
-        <v>58327</v>
+        <v>58003</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -713,19 +713,24 @@
           <t>1</t>
         </is>
       </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Grandalen, Sika, Frötuna, Upl, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>707203</v>
+        <v>707188</v>
       </c>
       <c r="R2" t="n">
-        <v>6624704</v>
+        <v>6624708</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,12 +754,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>05:06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>05:06</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,23 +789,638 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
+          <t>Indre Cepukaite</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Fågelinventering Sika 2026</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136480652</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>130659216</v>
+      </c>
+      <c r="B3" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Grandalen, Sika, Frötuna, Upl, Upl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>707203</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6624704</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Frötuna</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Indre Cepukaite</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
           <t>Via Indre Cepukaite</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr">
+      <c r="AY3" t="inlineStr">
         <is>
           <t>NVI Sika 4:37</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
+      <c r="AZ3" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/130659216</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>136480614</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58167</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Grandalen, Sika, Frötuna, Upl, Upl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>707152</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6624756</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Frötuna</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>05:12</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>05:12</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Indre Cepukaite</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Indre Cepukaite</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Fågelinventering Sika 2026</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136480614</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>136480594</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58162</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Grandalen, Sika, Frötuna, Upl, Upl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>707188</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6624740</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Frötuna</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>06:32</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-06-04</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>06:32</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Indre Cepukaite</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Indre Cepukaite</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Fågelinventering Sika 2026</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136480594</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>136480597</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58162</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>103023</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tofsmes</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lophophanes cristatus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Grandalen, Sika, Frötuna, Upl, Upl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>707213</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6624684</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Frötuna</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>16:51</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>16:51</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Indre Cepukaite</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Indre Cepukaite</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Fågelinventering Sika 2026</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136480597</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>136480812</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58729</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103055</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Grandalen, Sika, Frötuna, Upl, Upl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>707254</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6624731</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Frötuna</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>05:29</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-05-07</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>05:29</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Indre Cepukaite</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Indre Cepukaite</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Fågelinventering Sika 2026</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136480812</t>
         </is>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
